--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6899-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6899-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{881F64AA-E4F1-4E28-A6F1-0EB1F58B408E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A15481C-F391-4274-9A6B-1D1F5E10D3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{64AAF354-711C-4BEF-B248-97F99FAA3E74}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{20F725BC-FCF4-4112-AC7A-D950BB28AEF1}"/>
   </bookViews>
   <sheets>
     <sheet name="6899-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1457,23 +1457,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B005B070-EE2E-49E2-A155-32B1C79A8F8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{033C23A3-0531-4673-9059-B059C2DC6E9E}">
   <dimension ref="A1:R19"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1501,7 +1501,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1531,7 +1531,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1627,7 +1627,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2023</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2022</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39" t="s">
         <v>38</v>
       </c>
